--- a/files/energy/input/load_emulator/input_emulator_v2/2. multi_usage_probability_v2.xlsx
+++ b/files/energy/input/load_emulator/input_emulator_v2/2. multi_usage_probability_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rsericerca-my.sharepoint.com/personal/rollo_rse-web_it/Documents/Desktop/CACER simulator - public repo/CACER-simulator/files/energy/input/load_emulator/input_emulator_v2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="428" documentId="11_12FF3042CAB3BB62A4F5432140027D7DFA586928" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DECBB0A5-4D2B-48D3-A087-D386EB7C8626}"/>
+  <xr:revisionPtr revIDLastSave="434" documentId="11_12FF3042CAB3BB62A4F5432140027D7DFA586928" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29DF29B5-D26E-4325-B578-AED620D36853}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="working_day" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
     Information no available: equal to washing_machine</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{1BBB8FE1-3BA7-4F78-8233-20DF0153C5FF}">
+    <comment ref="K1" authorId="3" shapeId="0" xr:uid="{1BBB8FE1-3BA7-4F78-8233-20DF0153C5FF}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -221,7 +221,7 @@
     Information no available: equal to washing_machine</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{F4235117-6DC7-452E-81C4-9F43DEA85D01}">
+    <comment ref="K1" authorId="3" shapeId="0" xr:uid="{F4235117-6DC7-452E-81C4-9F43DEA85D01}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -366,9 +366,6 @@
     <t>dehumidifier</t>
   </si>
   <si>
-    <t>electric_hob</t>
-  </si>
-  <si>
     <t>iron</t>
   </si>
   <si>
@@ -410,12 +407,15 @@
   <si>
     <t>dryer</t>
   </si>
+  <si>
+    <t>induction_hob</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,12 +442,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -817,7 +811,7 @@
   <threadedComment ref="H1" dT="2026-03-24T15:03:57.74" personId="{45D9E587-2B70-4301-A733-75D37104F5C7}" id="{CFE95F9B-CB61-4A2A-BD9E-720DB2858EC8}">
     <text>Information no available: equal to washing_machine</text>
   </threadedComment>
-  <threadedComment ref="I1" dT="2026-03-24T15:04:07.09" personId="{45D9E587-2B70-4301-A733-75D37104F5C7}" id="{1BBB8FE1-3BA7-4F78-8233-20DF0153C5FF}">
+  <threadedComment ref="K1" dT="2026-03-24T15:04:07.09" personId="{45D9E587-2B70-4301-A733-75D37104F5C7}" id="{1BBB8FE1-3BA7-4F78-8233-20DF0153C5FF}">
     <text>Zenodo db</text>
   </threadedComment>
   <threadedComment ref="L1" dT="2026-03-24T15:04:22.76" personId="{45D9E587-2B70-4301-A733-75D37104F5C7}" id="{8AD0FC56-C82C-4999-8B91-0EAD48E2372E}">
@@ -867,7 +861,7 @@
   <threadedComment ref="H1" dT="2026-03-24T15:03:57.74" personId="{45D9E587-2B70-4301-A733-75D37104F5C7}" id="{96A91C7A-D5AC-42F7-AA7B-6251A8550818}">
     <text>Information no available: equal to washing_machine</text>
   </threadedComment>
-  <threadedComment ref="I1" dT="2026-03-24T15:04:07.09" personId="{45D9E587-2B70-4301-A733-75D37104F5C7}" id="{F4235117-6DC7-452E-81C4-9F43DEA85D01}">
+  <threadedComment ref="K1" dT="2026-03-24T15:04:07.09" personId="{45D9E587-2B70-4301-A733-75D37104F5C7}" id="{F4235117-6DC7-452E-81C4-9F43DEA85D01}">
     <text>Zenodo db</text>
   </threadedComment>
   <threadedComment ref="L1" dT="2026-03-24T15:04:22.76" personId="{45D9E587-2B70-4301-A733-75D37104F5C7}" id="{5340C758-FFC9-4444-B3A4-508083111668}">
@@ -915,10 +909,9 @@
     <col min="2" max="4" width="12.77734375" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="12.77734375" customWidth="1"/>
-    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="12.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="12.77734375" customWidth="1"/>
     <col min="14" max="14" width="19.44140625" bestFit="1" customWidth="1"/>
@@ -946,7 +939,7 @@
         <v>8</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>13</v>
@@ -955,34 +948,34 @@
         <v>1</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>4</v>
@@ -991,16 +984,16 @@
         <v>5</v>
       </c>
       <c r="T1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="V1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X1" s="5" t="s">
         <v>6</v>
@@ -1009,13 +1002,13 @@
         <v>9</v>
       </c>
       <c r="Z1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="AC1" s="5" t="s">
         <v>7</v>
@@ -1047,13 +1040,13 @@
         <v>3.6827195467422087E-2</v>
       </c>
       <c r="I2" s="2">
+        <v>0.72340425531914898</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.17073170731707321</v>
+      </c>
+      <c r="K2" s="2">
         <v>5.2386495925494762E-2</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.72340425531914898</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0.17073170731707321</v>
       </c>
       <c r="L2" s="2">
         <v>0.5</v>
@@ -1137,13 +1130,13 @@
         <v>0.46175637393767699</v>
       </c>
       <c r="I3" s="2">
+        <v>0.21276595744680851</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.23170731707317069</v>
+      </c>
+      <c r="K3" s="2">
         <v>0.20256111757857981</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.21276595744680851</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0.23170731707317069</v>
       </c>
       <c r="L3" s="2">
         <v>0.5</v>
@@ -1227,13 +1220,13 @@
         <v>0.34844192634560911</v>
       </c>
       <c r="I4" s="2">
+        <v>2.1276595744680851E-2</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.28048780487804881</v>
+      </c>
+      <c r="K4" s="2">
         <v>0.320139697322468</v>
-      </c>
-      <c r="J4" s="2">
-        <v>2.1276595744680851E-2</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0.28048780487804881</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -1317,13 +1310,13 @@
         <v>9.3484419263456089E-2</v>
       </c>
       <c r="I5" s="2">
+        <v>4.2553191489361701E-2</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.15853658536585369</v>
+      </c>
+      <c r="K5" s="2">
         <v>0.25029103608847503</v>
-      </c>
-      <c r="J5" s="2">
-        <v>4.2553191489361701E-2</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0.15853658536585369</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -1406,13 +1399,13 @@
         <v>5.3824362606232287E-2</v>
       </c>
       <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>7.3170731707317069E-2</v>
+      </c>
+      <c r="K6" s="2">
         <v>0.1187427240977881</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>7.3170731707317069E-2</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
@@ -1495,13 +1488,13 @@
         <v>5.6657223796033997E-3</v>
       </c>
       <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>4.878048780487805E-2</v>
+      </c>
+      <c r="K7" s="2">
         <v>4.190919674039581E-2</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>4.878048780487805E-2</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -1584,13 +1577,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>1.2195121951219509E-2</v>
+      </c>
+      <c r="K8" s="2">
         <v>1.280558789289872E-2</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1.2195121951219509E-2</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -1673,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>2.4390243902439029E-2</v>
+      </c>
+      <c r="K9" s="2">
         <v>1.164144353899884E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
-        <v>2.4390243902439029E-2</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -2231,8 +2224,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:AC13 C12:H13 C2:D11 F2:K9 Q2:W13 F10:H11 I10:K13">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="Y2:AC13 C12:H13 C2:D11 I2:K13 Q2:W13 F2:H11">
+    <cfRule type="colorScale" priority="36">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -2257,8 +2250,9 @@
     <col min="2" max="4" width="12.77734375" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="12.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="12.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="12.77734375" customWidth="1"/>
     <col min="14" max="14" width="19.44140625" bestFit="1" customWidth="1"/>
@@ -2286,7 +2280,7 @@
         <v>8</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>13</v>
@@ -2295,34 +2289,34 @@
         <v>1</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>4</v>
@@ -2331,16 +2325,16 @@
         <v>5</v>
       </c>
       <c r="T1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="V1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="W1" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X1" s="5" t="s">
         <v>6</v>
@@ -2349,13 +2343,13 @@
         <v>9</v>
       </c>
       <c r="Z1" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>24</v>
       </c>
       <c r="AC1" s="5" t="s">
         <v>7</v>
@@ -2387,13 +2381,13 @@
         <v>9.3220338983050849E-2</v>
       </c>
       <c r="I2" s="2">
+        <v>0.68421052631578949</v>
+      </c>
+      <c r="J2" s="2">
+        <v>0.32558139534883718</v>
+      </c>
+      <c r="K2" s="2">
         <v>4.6109510086455328E-2</v>
-      </c>
-      <c r="J2" s="2">
-        <v>0.68421052631578949</v>
-      </c>
-      <c r="K2" s="2">
-        <v>0.32558139534883718</v>
       </c>
       <c r="L2" s="2">
         <v>0.5</v>
@@ -2477,13 +2471,13 @@
         <v>0.42372881355932202</v>
       </c>
       <c r="I3" s="2">
+        <v>0.15789473684210531</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.23255813953488369</v>
+      </c>
+      <c r="K3" s="2">
         <v>0.17867435158501441</v>
-      </c>
-      <c r="J3" s="2">
-        <v>0.15789473684210531</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0.23255813953488369</v>
       </c>
       <c r="L3" s="2">
         <v>0.5</v>
@@ -2567,13 +2561,13 @@
         <v>0.33898305084745761</v>
       </c>
       <c r="I4" s="2">
+        <v>0.10526315789473679</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.16279069767441859</v>
+      </c>
+      <c r="K4" s="2">
         <v>0.34293948126801149</v>
-      </c>
-      <c r="J4" s="2">
-        <v>0.10526315789473679</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0.16279069767441859</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -2657,13 +2651,13 @@
         <v>0.1271186440677966</v>
       </c>
       <c r="I5" s="2">
+        <v>5.2631578947368418E-2</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.1395348837209302</v>
+      </c>
+      <c r="K5" s="2">
         <v>0.22478386167146969</v>
-      </c>
-      <c r="J5" s="2">
-        <v>5.2631578947368418E-2</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0.1395348837209302</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -2746,13 +2740,13 @@
         <v>8.4745762711864406E-3</v>
       </c>
       <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>9.3023255813953487E-2</v>
+      </c>
+      <c r="K6" s="2">
         <v>0.1325648414985591</v>
-      </c>
-      <c r="J6" s="2">
-        <v>0</v>
-      </c>
-      <c r="K6" s="2">
-        <v>9.3023255813953487E-2</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
@@ -2835,13 +2829,13 @@
         <v>8.4745762711864406E-3</v>
       </c>
       <c r="I7" s="2">
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <v>2.3255813953488368E-2</v>
+      </c>
+      <c r="K7" s="2">
         <v>5.7636887608069162E-2</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-      <c r="K7" s="2">
-        <v>2.3255813953488368E-2</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
@@ -2924,13 +2918,13 @@
         <v>0</v>
       </c>
       <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>2.3255813953488368E-2</v>
+      </c>
+      <c r="K8" s="2">
         <v>1.4409221902017291E-2</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>2.3255813953488368E-2</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -3013,13 +3007,13 @@
         <v>0</v>
       </c>
       <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
         <v>2.881844380403458E-3</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2">
-        <v>0</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
